--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>

--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="20760" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
@@ -70,10 +70,10 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>英雄1</t>
-  </si>
-  <si>
-    <t>类型1</t>
+    <t>神力恩泽</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
   </si>
   <si>
     <t>1.11,1.12</t>

--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20760" windowHeight="7545"/>
+    <workbookView windowHeight="17175"/>
   </bookViews>
   <sheets>
-    <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="英雄表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -82,34 +80,67 @@
     <t>1,2,3,4,5</t>
   </si>
   <si>
-    <t>英雄2</t>
-  </si>
-  <si>
-    <t>类型2</t>
-  </si>
-  <si>
-    <t>英雄3</t>
-  </si>
-  <si>
-    <t>类型3</t>
-  </si>
-  <si>
-    <t>英雄4</t>
-  </si>
-  <si>
-    <t>类型4</t>
-  </si>
-  <si>
-    <t>英雄5</t>
-  </si>
-  <si>
-    <t>类型5</t>
-  </si>
-  <si>
-    <t>英雄6</t>
-  </si>
-  <si>
-    <t>类型6</t>
+    <t>烈焰之心</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>暗影之刃</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>自然之语</t>
+  </si>
+  <si>
+    <t>德鲁伊</t>
+  </si>
+  <si>
+    <t>钢铁之盾</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>风暴之眼</t>
+  </si>
+  <si>
+    <t>萨满</t>
+  </si>
+  <si>
+    <t>光明使者</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>霜寒之握</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>大地之怒</t>
+  </si>
+  <si>
+    <t>元素使</t>
+  </si>
+  <si>
+    <t>星辰之佑</t>
+  </si>
+  <si>
+    <t>圣骑</t>
+  </si>
+  <si>
+    <t>星辰之佑11</t>
+  </si>
+  <si>
+    <t>圣骑11</t>
   </si>
 </sst>
 </file>
@@ -122,7 +153,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,161 +615,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -784,7 +815,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -794,9 +825,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -804,39 +835,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -868,7 +899,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -903,135 +933,171 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1043,197 +1109,310 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
-  <cols>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>1.1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1">
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17175"/>
+    <workbookView windowWidth="25185" windowHeight="7995"/>
   </bookViews>
   <sheets>
-    <sheet name="英雄表" sheetId="1" r:id="rId1"/>
+    <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,14 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,148 +609,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1111,6 +1104,10 @@
   <sheetPr/>
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="6" max="7" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">

--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -26,8 +26,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+英雄属性表关联</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -48,6 +80,9 @@
   </si>
   <si>
     <t>ClientExe3</t>
+  </si>
+  <si>
+    <t>AttrId</t>
   </si>
   <si>
     <t>int</t>
@@ -153,7 +188,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +339,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1102,14 +1148,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="5" max="5" width="10.375" customWidth="1"/>
     <col min="6" max="7" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1131,39 +1177,45 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -1172,21 +1224,24 @@
         <v>1.1</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1195,21 +1250,24 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1218,21 +1276,24 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -1241,21 +1302,24 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -1264,21 +1328,24 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1287,21 +1354,24 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -1310,21 +1380,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -1333,21 +1406,24 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -1356,21 +1432,24 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -1379,21 +1458,24 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -1402,14 +1484,18 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="7995"/>
+    <workbookView windowHeight="8130"/>
   </bookViews>
   <sheets>
     <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -121,9 +121,6 @@
     <t>法师</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>暗影之刃</t>
   </si>
   <si>
@@ -176,6 +173,9 @@
   </si>
   <si>
     <t>圣骑11</t>
+  </si>
+  <si>
+    <t>外星人</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="5" max="5" width="10.375" customWidth="1"/>
@@ -1249,11 +1249,11 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1264,22 +1264,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -1290,10 +1290,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -1301,11 +1301,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -1316,22 +1316,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1342,22 +1342,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1368,10 +1368,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
         <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -1379,11 +1379,11 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1394,22 +1394,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -1420,22 +1420,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -1446,10 +1446,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -1457,11 +1457,11 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -1472,10 +1472,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -1483,14 +1483,40 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
       </c>
       <c r="H13">
         <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="8130"/>
+    <workbookView windowWidth="30585" windowHeight="8985"/>
   </bookViews>
   <sheets>
     <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="H1" authorId="0">
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Administrator:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>英雄初始技能</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -73,13 +95,7 @@
     <t>IsSuper</t>
   </si>
   <si>
-    <t>ClientExe</t>
-  </si>
-  <si>
-    <t>ClientExe2</t>
-  </si>
-  <si>
-    <t>ClientExe3</t>
+    <t>SkillList</t>
   </si>
   <si>
     <t>AttrId</t>
@@ -94,25 +110,19 @@
     <t>boolean</t>
   </si>
   <si>
+    <t>number[]</t>
+  </si>
+  <si>
     <t>number</t>
   </si>
   <si>
-    <t>number[]</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>神力恩泽</t>
   </si>
   <si>
     <t>圣骑士</t>
   </si>
   <si>
-    <t>1.11,1.12</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5</t>
+    <t>1,2,3,4</t>
   </si>
   <si>
     <t>烈焰之心</t>
@@ -1148,14 +1158,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="5" max="5" width="10.375" customWidth="1"/>
-    <col min="6" max="7" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1174,348 +1183,264 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1.1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>0</v>
+      <c r="E4" t="s">
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="E5" t="s">
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>0</v>
+      <c r="E6" t="s">
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
-      <c r="E7">
-        <v>0</v>
+      <c r="E7" t="s">
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="E8" t="s">
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="E9" t="s">
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
-      <c r="E10">
-        <v>0</v>
+      <c r="E10" t="s">
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="E11" t="s">
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>0</v>
+      <c r="E12" t="s">
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="E13">
-        <v>0</v>
+      <c r="E13" t="s">
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E14">
-        <v>0</v>
+      <c r="E14" t="s">
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
         <v>12</v>
       </c>
     </row>

--- a/trunk/plan/excel/英雄表.xlsx
+++ b/trunk/plan/excel/英雄表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30585" windowHeight="8985"/>
+    <workbookView windowWidth="22350" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="HeroBookCFG" sheetId="1" r:id="rId1"/>
